--- a/documentos/ESQUEMA GRANJA.xlsx
+++ b/documentos/ESQUEMA GRANJA.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23029"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Desktop\Gallinas SG&amp;CR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rosmer\Desktop\PROYECTO\SIGEAGRO\documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BFC3BF-C700-4272-B7C6-86DE62197689}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2370" windowHeight="0"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="19530" windowHeight="15090" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GALPONES" sheetId="1" r:id="rId1"/>
     <sheet name="SEPARADORES" sheetId="2" r:id="rId2"/>
+    <sheet name="Tabla Ejemplo Recolección" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -132,7 +134,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -549,69 +551,6 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -633,9 +572,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -676,6 +612,72 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -955,45 +957,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:P28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:16" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="51" t="s">
+    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="2:16" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B4" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="K4" s="54" t="s">
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="K4" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="56"/>
-    </row>
-    <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:16" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="84"/>
+    </row>
+    <row r="6" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="2:16" ht="31" x14ac:dyDescent="0.55000000000000004">
       <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="80" t="s">
+      <c r="G7" s="58" t="s">
         <v>33</v>
       </c>
       <c r="L7" s="14" t="s">
@@ -1001,65 +1003,65 @@
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="81" t="s">
+      <c r="O7" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="82" t="s">
+      <c r="P7" s="60" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C8" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="5">
         <v>1553</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="E8" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="84"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="62"/>
       <c r="L8" s="19" t="s">
         <v>2</v>
       </c>
       <c r="M8" s="20">
         <v>2195</v>
       </c>
-      <c r="N8" s="78" t="s">
+      <c r="N8" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="89"/>
-      <c r="P8" s="85"/>
-    </row>
-    <row r="9" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="O8" s="67"/>
+      <c r="P8" s="63"/>
+    </row>
+    <row r="9" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="5">
         <v>3585</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E9" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="83"/>
-      <c r="G9" s="84"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="62"/>
       <c r="L9" s="19" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="20">
         <v>2043</v>
       </c>
-      <c r="N9" s="78" t="s">
+      <c r="N9" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="O9" s="89"/>
-      <c r="P9" s="85"/>
-    </row>
-    <row r="10" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="O9" s="67"/>
+      <c r="P9" s="63"/>
+    </row>
+    <row r="10" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C10" s="6"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="75"/>
+      <c r="E10" s="53"/>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="L10" s="19" t="s">
@@ -1068,16 +1070,16 @@
       <c r="M10" s="20">
         <v>3778</v>
       </c>
-      <c r="N10" s="78" t="s">
+      <c r="N10" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="89"/>
-      <c r="P10" s="85"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O10" s="67"/>
+      <c r="P10" s="63"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C11" s="6"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="75"/>
+      <c r="E11" s="53"/>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="L11" s="15"/>
@@ -1086,15 +1088,15 @@
       <c r="O11" s="16"/>
       <c r="P11" s="17"/>
     </row>
-    <row r="12" spans="2:16" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="75"/>
+      <c r="E12" s="53"/>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
-      <c r="L12" s="72" t="s">
+      <c r="L12" s="50" t="s">
         <v>5</v>
       </c>
       <c r="M12" s="16"/>
@@ -1102,34 +1104,34 @@
       <c r="O12" s="16"/>
       <c r="P12" s="17"/>
     </row>
-    <row r="13" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="8">
         <v>2137</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="87"/>
-      <c r="G13" s="85"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="63"/>
       <c r="L13" s="18" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="5">
         <v>1181</v>
       </c>
-      <c r="N13" s="78" t="s">
+      <c r="N13" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="O13" s="88"/>
-      <c r="P13" s="86"/>
-    </row>
-    <row r="14" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="O13" s="66"/>
+      <c r="P13" s="64"/>
+    </row>
+    <row r="14" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="75"/>
+      <c r="E14" s="53"/>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="L14" s="18" t="s">
@@ -1138,16 +1140,16 @@
       <c r="M14" s="5">
         <v>918</v>
       </c>
-      <c r="N14" s="78" t="s">
+      <c r="N14" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="88"/>
-      <c r="P14" s="86"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O14" s="66"/>
+      <c r="P14" s="64"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="75"/>
+      <c r="E15" s="53"/>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="L15" s="15"/>
@@ -1156,7 +1158,7 @@
       <c r="O15" s="16"/>
       <c r="P15" s="17"/>
     </row>
-    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C16" s="9" t="s">
         <v>7</v>
       </c>
@@ -1164,11 +1166,11 @@
         <f>+D8+D9+D13</f>
         <v>7275</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="64"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
       <c r="L16" s="9" t="s">
         <v>7</v>
       </c>
@@ -1176,157 +1178,157 @@
         <f>+M8+M9+M13+M10+M14</f>
         <v>10115</v>
       </c>
-      <c r="N16" s="77" t="s">
+      <c r="N16" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="O16" s="63"/>
-      <c r="P16" s="64"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O16" s="42"/>
+      <c r="P16" s="43"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D17" s="2"/>
     </row>
-    <row r="19" spans="2:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="B19" s="57" t="s">
+    <row r="19" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+      <c r="B19" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
-      <c r="K19" s="57" t="s">
+      <c r="K19" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-    </row>
-    <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="45" t="s">
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+    </row>
+    <row r="20" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="46"/>
+      <c r="D21" s="74"/>
       <c r="E21" s="22">
         <v>0.33333333333333331</v>
       </c>
-      <c r="L21" s="58" t="s">
+      <c r="L21" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="59"/>
+      <c r="M21" s="87"/>
       <c r="N21" s="25">
         <v>0.375</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="47"/>
-      <c r="D22" s="48"/>
+    <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="75"/>
+      <c r="D22" s="76"/>
       <c r="E22" s="23">
         <v>0.45833333333333331</v>
       </c>
-      <c r="L22" s="60"/>
-      <c r="M22" s="61"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="89"/>
       <c r="N22" s="26">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="49" t="s">
+    <row r="23" spans="2:15" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C23" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="50"/>
+      <c r="D23" s="78"/>
       <c r="E23" s="24">
         <v>0.64583333333333337</v>
       </c>
-      <c r="L23" s="41" t="s">
+      <c r="L23" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="M23" s="42"/>
+      <c r="M23" s="70"/>
       <c r="N23" s="27">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L24" s="43"/>
-      <c r="M24" s="44"/>
+    <row r="24" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L24" s="71"/>
+      <c r="M24" s="72"/>
       <c r="N24" s="28">
         <v>0.625</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="71" t="s">
+    <row r="26" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="K26" s="71" t="s">
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="K26" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="69" t="s">
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B27" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="70" t="s">
+      <c r="C27" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="65"/>
-      <c r="K27" s="69" t="s">
+      <c r="D27" s="44"/>
+      <c r="K27" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="L27" s="70" t="s">
+      <c r="L27" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="M27" s="65"/>
-    </row>
-    <row r="28" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="66">
+      <c r="M27" s="44"/>
+    </row>
+    <row r="28" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="45">
         <v>21</v>
       </c>
-      <c r="C28" s="67" t="s">
+      <c r="C28" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="66">
+      <c r="K28" s="45">
         <v>29</v>
       </c>
-      <c r="L28" s="67" t="s">
+      <c r="L28" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M28" s="68" t="s">
+      <c r="M28" s="47" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="K19:O19"/>
+    <mergeCell ref="L21:M22"/>
     <mergeCell ref="K26:M26"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="L23:M24"/>
     <mergeCell ref="C21:D22"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="K4:O4"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="K19:O19"/>
-    <mergeCell ref="L21:M22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C5:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="5" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="3:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="3:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C6" s="29" t="s">
         <v>16</v>
       </c>
@@ -1340,8 +1342,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C8" s="32" t="s">
         <v>22</v>
       </c>
@@ -1358,7 +1360,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C9" s="35" t="s">
         <v>20</v>
       </c>
@@ -1375,7 +1377,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C10" s="35" t="s">
         <v>21</v>
       </c>
@@ -1392,7 +1394,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C11" s="35" t="s">
         <v>15</v>
       </c>
@@ -1409,7 +1411,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C12" s="35" t="s">
         <v>25</v>
       </c>
@@ -1426,7 +1428,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C13" s="35" t="s">
         <v>23</v>
       </c>
@@ -1443,7 +1445,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C14" s="35" t="s">
         <v>24</v>
       </c>
@@ -1460,7 +1462,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C15" s="38" t="s">
         <v>26</v>
       </c>
@@ -1477,11 +1479,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="62">
+      <c r="F16" s="41">
         <f>SUM(F8:F15)</f>
         <v>600</v>
       </c>
@@ -1490,4 +1492,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8DB395E-3EDC-4BC5-9F33-E2C0642ADF72}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>